--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484557_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484557_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7058</v>
+        <v>2.1315</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6006</v>
+        <v>2.1749</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1052</v>
+        <v>-0.0434</v>
       </c>
       <c r="G2" t="n">
         <v>-0.7485000000000001</v>
@@ -610,13 +610,13 @@
         <v>2.1991</v>
       </c>
       <c r="S2" t="n">
-        <v>1.275</v>
+        <v>0.7006</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1705</v>
+        <v>0.7447</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1045</v>
+        <v>-0.0441</v>
       </c>
       <c r="V2" t="n">
         <v>2.7292</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6249</v>
+        <v>1.0402</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4779</v>
+        <v>0.6702</v>
       </c>
       <c r="F4" t="n">
-        <v>0.147</v>
+        <v>0.37</v>
       </c>
       <c r="G4" t="n">
         <v>-0.6552</v>
@@ -766,13 +766,13 @@
         <v>1.2828</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3174</v>
+        <v>-0.9022</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7157</v>
+        <v>-0.5234</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6017</v>
+        <v>-0.3788</v>
       </c>
       <c r="V4" t="n">
         <v>1.3147</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. SORO VILLANUEVA</t>
+          <t>O. FORNER LUCEA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2824</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3384</v>
+        <v>-0.0334</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.056</v>
+        <v>0.1222</v>
       </c>
       <c r="G5" t="n">
-        <v>3.1699</v>
+        <v>0.0613</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5833</v>
+        <v>-0.0669</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5866</v>
+        <v>0.1282</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5579</v>
+        <v>0.0217</v>
       </c>
       <c r="K5" t="n">
-        <v>2.907</v>
+        <v>0.0217</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6509</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3879</v>
+        <v>0.0397</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3237</v>
+        <v>-0.0885</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0643</v>
+        <v>0.1282</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.6493</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0995</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9738</v>
+        <v>0.0275</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2074</v>
+        <v>-0.0551</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2336</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.212</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.5339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. FORNER LUCEA</t>
+          <t>R. SORO VILLANUEVA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0393</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0334</v>
+        <v>1.2807</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0727</v>
+        <v>-1.8578</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0613</v>
+        <v>3.1699</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0669</v>
+        <v>2.5833</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1282</v>
+        <v>0.5866</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0217</v>
+        <v>3.5579</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0217</v>
+        <v>2.907</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.6509</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0397</v>
+        <v>-0.3879</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0885</v>
+        <v>-0.3237</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1282</v>
+        <v>-0.0643</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-1.6493</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.0995</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.022</v>
+        <v>0.1143</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0551</v>
+        <v>0.1497</v>
       </c>
       <c r="U6" t="n">
-        <v>0.033</v>
+        <v>-0.0355</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-2.212</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.5339</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-1.5363</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2307</v>
+        <v>-0.9038</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5086000000000001</v>
+        <v>-0.6325</v>
       </c>
       <c r="G7" t="n">
         <v>-1.3973</v>
@@ -1000,13 +1000,13 @@
         <v>0.5498</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0532</v>
+        <v>0.2562</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8416</v>
+        <v>0.1686</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2115</v>
+        <v>0.0877</v>
       </c>
       <c r="V7" t="n">
         <v>-0.945</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. VANOUKIA</t>
+          <t>A. ALVAREZ LENCINA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8792</v>
+        <v>-1.9765</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2241</v>
+        <v>0.175</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3449</v>
+        <v>-2.1515</v>
       </c>
       <c r="G8" t="n">
-        <v>-5.5392</v>
+        <v>-1.8224</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.3785</v>
+        <v>-0.6682</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.1607</v>
+        <v>-1.1541</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.0324</v>
+        <v>-0.1859</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.8337</v>
+        <v>-0.1859</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.1987</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.5068</v>
+        <v>-1.6365</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.5448</v>
+        <v>-0.4824</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.962</v>
+        <v>-1.1541</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9163</v>
+        <v>0.5498</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7489</v>
+        <v>0.5498</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7747000000000001</v>
+        <v>0.2515</v>
       </c>
       <c r="T8" t="n">
-        <v>0.73</v>
+        <v>0.3609</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0447</v>
+        <v>-0.1094</v>
       </c>
       <c r="V8" t="n">
-        <v>1.969</v>
+        <v>-0.9554</v>
       </c>
       <c r="W8" t="n">
-        <v>1.9109</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0581</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6509</v>
+        <v>-2.511</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4005</v>
+        <v>-1.1121</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2503</v>
+        <v>-1.399</v>
       </c>
       <c r="G9" t="n">
         <v>-3.125</v>
@@ -1156,13 +1156,13 @@
         <v>2.0158</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9635</v>
+        <v>1.1033</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4744</v>
+        <v>0.7628</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4891</v>
+        <v>0.3405</v>
       </c>
       <c r="V9" t="n">
         <v>-1.5889</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. ALVAREZ LENCINA</t>
+          <t>M. VANOUKIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7047</v>
+        <v>-2.5304</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5531</v>
+        <v>-2.801</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1515</v>
+        <v>0.2706</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8224</v>
+        <v>-5.5392</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6682</v>
+        <v>-3.3785</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1541</v>
+        <v>-2.1607</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1859</v>
+        <v>-3.0324</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1859</v>
+        <v>-1.8337</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-1.1987</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6365</v>
+        <v>-2.5068</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4824</v>
+        <v>-1.5448</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1541</v>
+        <v>-0.962</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5498</v>
+        <v>0.9163</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5498</v>
+        <v>2.7489</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4766</v>
+        <v>0.1235</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3673</v>
+        <v>0.1531</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1094</v>
+        <v>-0.0296</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9554</v>
+        <v>1.969</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.9109</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.9554</v>
+        <v>0.0581</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. ROMAN MORA</t>
+          <t>E. NAVARRO VALDES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3861</v>
+        <v>-2.6719</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9737</v>
+        <v>-1.5141</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4124</v>
+        <v>-1.1578</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.3812</v>
+        <v>-2.4356</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.7593</v>
+        <v>-0.0125</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6219</v>
+        <v>-2.4232</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3968</v>
+        <v>0.5535</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1609</v>
+        <v>2.3993</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5577</v>
+        <v>-1.8458</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9845</v>
+        <v>-2.9891</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.9202</v>
+        <v>-2.4118</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0643</v>
+        <v>-0.5774</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1833</v>
+        <v>1.0995</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R11" t="n">
-        <v>1.0995</v>
+        <v>2.9321</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0406</v>
+        <v>-0.4489</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6606</v>
+        <v>-0.2454</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.38</v>
+        <v>-0.2035</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1475</v>
+        <v>-0.8869</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.0104</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1475</v>
+        <v>-0.8973</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E. NAVARRO VALDES</t>
+          <t>F. ROMAN MORA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.7599</v>
+        <v>-3.1882</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6269</v>
+        <v>-1.7263</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.133</v>
+        <v>-1.4619</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.4356</v>
+        <v>-2.3812</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0125</v>
+        <v>-1.7593</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.4232</v>
+        <v>-0.6219</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5535</v>
+        <v>-0.3968</v>
       </c>
       <c r="K12" t="n">
-        <v>2.3993</v>
+        <v>0.1609</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.8458</v>
+        <v>-0.5577</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.9891</v>
+        <v>-1.9845</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.4118</v>
+        <v>-1.9202</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5774</v>
+        <v>-0.0643</v>
       </c>
       <c r="P12" t="n">
+        <v>0.1833</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-0.9163</v>
+      </c>
+      <c r="R12" t="n">
         <v>1.0995</v>
       </c>
-      <c r="Q12" t="n">
-        <v>-1.8326</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.9321</v>
-      </c>
       <c r="S12" t="n">
-        <v>-1.5369</v>
+        <v>-0.8428</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.3582</v>
+        <v>-0.4133</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1787</v>
+        <v>-0.4295</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.8869</v>
+        <v>-0.1475</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0104</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.8973</v>
+        <v>-0.1475</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.9827</v>
+        <v>-3.9083</v>
       </c>
       <c r="E13" t="n">
         <v>-0.9912</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.9915</v>
+        <v>-2.9172</v>
       </c>
       <c r="G13" t="n">
         <v>1.455</v>
@@ -1468,13 +1468,13 @@
         <v>0.9163</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1959</v>
+        <v>0.2702</v>
       </c>
       <c r="T13" t="n">
         <v>-0.0196</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2154</v>
+        <v>0.2898</v>
       </c>
       <c r="V13" t="n">
         <v>-3.8009</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.4334</v>
+        <v>-4.969</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.6695</v>
+        <v>-2.2299</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.7639</v>
+        <v>-2.7391</v>
       </c>
       <c r="G14" t="n">
         <v>-3.1596</v>
@@ -1546,13 +1546,13 @@
         <v>2.0158</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9367</v>
+        <v>-0.4723</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6252</v>
+        <v>-0.1855</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3116</v>
+        <v>-0.2868</v>
       </c>
       <c r="V14" t="n">
         <v>-1.5204</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-19.6086</v>
+        <v>-19.3328</v>
       </c>
       <c r="E15" t="n">
-        <v>-6.010900000000001</v>
+        <v>-5.735700000000001</v>
       </c>
       <c r="F15" t="n">
         <v>-13.5974</v>
@@ -1597,7 +1597,7 @@
         <v>-9.7776</v>
       </c>
       <c r="J15" t="n">
-        <v>1.933600000000001</v>
+        <v>1.9336</v>
       </c>
       <c r="K15" t="n">
         <v>6.579800000000001</v>
@@ -1612,7 +1612,7 @@
         <v>-12.1049</v>
       </c>
       <c r="O15" t="n">
-        <v>-5.131400000000001</v>
+        <v>-5.131399999999999</v>
       </c>
       <c r="P15" t="n">
         <v>1.8326</v>
@@ -1624,13 +1624,13 @@
         <v>17.4094</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.09409999999999974</v>
+        <v>0.1809</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6221999999999999</v>
+        <v>0.8975</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7168</v>
+        <v>-0.7166</v>
       </c>
       <c r="V15" t="n">
         <v>-6.0441</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>9.1075</v>
+        <v>9.4528</v>
       </c>
       <c r="E16" t="n">
-        <v>9.4892</v>
+        <v>9.6815</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3817</v>
+        <v>-0.2287</v>
       </c>
       <c r="G16" t="n">
         <v>10.0013</v>
@@ -1702,13 +1702,13 @@
         <v>2.5656</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3312</v>
+        <v>0.0141</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0384</v>
+        <v>0.1539</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2927</v>
+        <v>-0.1397</v>
       </c>
       <c r="V16" t="n">
         <v>-2.212</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ CAMPINA</t>
+          <t>D. HOYAS PEREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.8851</v>
+        <v>4.5882</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5844</v>
+        <v>3.8182</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3007</v>
+        <v>0.77</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.1065</v>
+        <v>2.3928</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6705</v>
+        <v>0.8702</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.436</v>
+        <v>1.5226</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.4253</v>
+        <v>2.3656</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9721</v>
+        <v>0.907</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.3974</v>
+        <v>1.4586</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6811</v>
+        <v>0.0271</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.6425</v>
+        <v>-0.0368</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9614</v>
+        <v>0.064</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9163</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8326</v>
+        <v>1.4661</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9525</v>
+        <v>-0.2836</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8032</v>
+        <v>0.1177</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1493</v>
+        <v>-0.4012</v>
       </c>
       <c r="V17" t="n">
-        <v>4.1229</v>
+        <v>2.8455</v>
       </c>
       <c r="W17" t="n">
-        <v>4.1229</v>
+        <v>3.1674</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. HOYAS PEREZ</t>
+          <t>E. CHOFRE TARREGA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.8831</v>
+        <v>3.1838</v>
       </c>
       <c r="E18" t="n">
-        <v>3.2412</v>
+        <v>1.5851</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6418</v>
+        <v>1.5987</v>
       </c>
       <c r="G18" t="n">
-        <v>2.3928</v>
+        <v>0.1302</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8702</v>
+        <v>1.1686</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5226</v>
+        <v>-1.0384</v>
       </c>
       <c r="J18" t="n">
-        <v>2.3656</v>
+        <v>0.0542</v>
       </c>
       <c r="K18" t="n">
-        <v>0.907</v>
+        <v>1.2847</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4586</v>
+        <v>-1.2305</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0271</v>
+        <v>0.076</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0368</v>
+        <v>-0.1161</v>
       </c>
       <c r="O18" t="n">
-        <v>0.064</v>
+        <v>0.1922</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3665</v>
+        <v>1.2828</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4661</v>
+        <v>1.2828</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9887</v>
+        <v>0.1923</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4593</v>
+        <v>0.264</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5294</v>
+        <v>-0.0717</v>
       </c>
       <c r="V18" t="n">
-        <v>2.8455</v>
+        <v>1.5785</v>
       </c>
       <c r="W18" t="n">
-        <v>3.1674</v>
+        <v>1.267</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3219</v>
+        <v>0.3115</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. CHOFRE TARREGA</t>
+          <t>L. RODRIGUEZ CAMPINA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.6942</v>
+        <v>3.1159</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3928</v>
+        <v>1.8152</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3014</v>
+        <v>1.3007</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1302</v>
+        <v>-2.1065</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1686</v>
+        <v>-0.6705</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0384</v>
+        <v>-1.436</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0542</v>
+        <v>-1.4253</v>
       </c>
       <c r="K19" t="n">
-        <v>1.2847</v>
+        <v>0.9721</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2305</v>
+        <v>-2.3974</v>
       </c>
       <c r="M19" t="n">
-        <v>0.076</v>
+        <v>-0.6811</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1161</v>
+        <v>-1.6425</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1922</v>
+        <v>0.9614</v>
       </c>
       <c r="P19" t="n">
-        <v>1.2828</v>
+        <v>0.9163</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2828</v>
+        <v>1.8326</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2973</v>
+        <v>0.1833</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0717</v>
+        <v>0.034</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3689</v>
+        <v>0.1493</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5785</v>
+        <v>4.1229</v>
       </c>
       <c r="W19" t="n">
-        <v>1.267</v>
+        <v>4.1229</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3115</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>H. MARCO LOPEZ</t>
+          <t>E. DENIA VIVANCOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.9613</v>
+        <v>2.5496</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6445</v>
+        <v>0.4281</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3169</v>
+        <v>2.1216</v>
       </c>
       <c r="G20" t="n">
-        <v>2.7952</v>
+        <v>-0.6236</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0415</v>
+        <v>-2.4764</v>
       </c>
       <c r="I20" t="n">
-        <v>2.7537</v>
+        <v>1.8528</v>
       </c>
       <c r="J20" t="n">
-        <v>2.7772</v>
+        <v>-0.457</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6002999999999999</v>
+        <v>-1.3162</v>
       </c>
       <c r="L20" t="n">
-        <v>2.1769</v>
+        <v>0.8592</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0179</v>
+        <v>-0.1667</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5588</v>
+        <v>-1.1602</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5768</v>
+        <v>0.9935</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.8326</v>
+        <v>2.1991</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.6651</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8326</v>
+        <v>2.1991</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2683</v>
+        <v>-0.2928</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0565</v>
+        <v>-0.382</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2117</v>
+        <v>0.0892</v>
       </c>
       <c r="V20" t="n">
         <v>1.267</v>
       </c>
       <c r="W20" t="n">
-        <v>1.5889</v>
+        <v>1.267</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. DENIA VIVANCOS</t>
+          <t>H. MARCO LOPEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.7672</v>
+        <v>2.0152</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0527</v>
+        <v>0.6445</v>
       </c>
       <c r="F21" t="n">
-        <v>1.82</v>
+        <v>1.3707</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6236</v>
+        <v>2.7952</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.4764</v>
+        <v>0.0415</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8528</v>
+        <v>2.7537</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.457</v>
+        <v>2.7772</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.3162</v>
+        <v>0.6002999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>0.8592</v>
+        <v>2.1769</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1667</v>
+        <v>0.0179</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1602</v>
+        <v>-0.5588</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9935</v>
+        <v>0.5768</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1991</v>
+        <v>-1.8326</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.6651</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1991</v>
+        <v>1.8326</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0752</v>
+        <v>-0.2144</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8627</v>
+        <v>-0.0565</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2125</v>
+        <v>-0.1578</v>
       </c>
       <c r="V21" t="n">
         <v>1.267</v>
       </c>
       <c r="W21" t="n">
-        <v>1.267</v>
+        <v>1.5889</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="22">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4946</v>
+        <v>0.3094</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.2154</v>
+        <v>0.1692</v>
       </c>
       <c r="F23" t="n">
-        <v>0.71</v>
+        <v>0.1402</v>
       </c>
       <c r="G23" t="n">
         <v>1.422</v>
@@ -2248,13 +2248,13 @@
         <v>1.4661</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3554</v>
+        <v>0.1702</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6976</v>
+        <v>-0.313</v>
       </c>
       <c r="U23" t="n">
-        <v>1.053</v>
+        <v>0.4832</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1509</v>
+        <v>-0.4365</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.4171</v>
+        <v>-0.8017</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2662</v>
+        <v>0.3653</v>
       </c>
       <c r="G24" t="n">
         <v>3.5847</v>
@@ -2326,13 +2326,13 @@
         <v>1.0995</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3406</v>
+        <v>0.0551</v>
       </c>
       <c r="T24" t="n">
-        <v>0.8228</v>
+        <v>0.4382</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4822</v>
+        <v>-0.3831</v>
       </c>
       <c r="V24" t="n">
         <v>0.3219</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.8015</v>
+        <v>-0.7766999999999999</v>
       </c>
       <c r="E25" t="n">
         <v>-0.7295</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.0472</v>
       </c>
       <c r="G25" t="n">
         <v>-0.7079</v>
@@ -2404,13 +2404,13 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0936</v>
+        <v>-0.0688</v>
       </c>
       <c r="T25" t="n">
         <v>-0.1101</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0165</v>
+        <v>0.0413</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.9119</v>
+        <v>-1.5136</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.4707</v>
+        <v>-1.0476</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.4413</v>
+        <v>-0.466</v>
       </c>
       <c r="G26" t="n">
         <v>-0.8032</v>
@@ -2482,13 +2482,13 @@
         <v>0.3665</v>
       </c>
       <c r="S26" t="n">
-        <v>1.3756</v>
+        <v>0.7739</v>
       </c>
       <c r="T26" t="n">
-        <v>0.8416</v>
+        <v>0.2647</v>
       </c>
       <c r="U26" t="n">
-        <v>0.534</v>
+        <v>0.5092</v>
       </c>
       <c r="V26" t="n">
         <v>-0.9346</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.8958</v>
+        <v>-3.8142</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.4448</v>
+        <v>-3.5409</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.4511</v>
+        <v>-0.2733</v>
       </c>
       <c r="G27" t="n">
         <v>-2.3579</v>
@@ -2560,13 +2560,13 @@
         <v>1.4661</v>
       </c>
       <c r="S27" t="n">
-        <v>0.1243</v>
+        <v>0.2059</v>
       </c>
       <c r="T27" t="n">
-        <v>0.402</v>
+        <v>0.3058</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.2777</v>
+        <v>-0.0999</v>
       </c>
       <c r="V27" t="n">
         <v>-2.212</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>19.6082</v>
+        <v>20.2492</v>
       </c>
       <c r="E28" t="n">
-        <v>13.59719999999999</v>
+        <v>13.5974</v>
       </c>
       <c r="F28" t="n">
-        <v>6.010899999999999</v>
+        <v>6.652</v>
       </c>
       <c r="G28" t="n">
         <v>15.3024</v>
@@ -2638,13 +2638,13 @@
         <v>15.577</v>
       </c>
       <c r="S28" t="n">
-        <v>0.09409999999999999</v>
+        <v>0.7352000000000001</v>
       </c>
       <c r="T28" t="n">
-        <v>0.7167</v>
+        <v>0.7167000000000001</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.6223000000000003</v>
+        <v>0.01880000000000008</v>
       </c>
       <c r="V28" t="n">
         <v>6.0442</v>
